--- a/artfynd/A 30193-2026 artfynd.xlsx
+++ b/artfynd/A 30193-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130466980</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848866</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130467204</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130467241</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395849</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395958</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393790</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393416</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134394086</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134394515</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395593</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1895,6 +1955,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395831</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393447</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +2173,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748895</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2205,6 +2280,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393403</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2306,6 +2386,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395412</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2407,6 +2492,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395792</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395383</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130467122</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2710,6 +2810,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848655</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2811,6 +2916,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130467034</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2912,6 +3022,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130467073</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3013,6 +3128,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130467163</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3118,6 +3238,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134394493</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3219,6 +3344,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848714</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3320,6 +3450,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395853</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3421,6 +3556,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848794</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3522,6 +3662,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126760235</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3623,6 +3768,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826562</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3724,6 +3874,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848641</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3825,6 +3980,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848683</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3926,6 +4086,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130466830</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4027,6 +4192,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130467166</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4128,6 +4298,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393712</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4229,6 +4404,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393727</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4330,6 +4510,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395374</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4431,6 +4616,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395624</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4532,6 +4722,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395981</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4649,6 +4844,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848899</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4766,6 +4966,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848842</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4883,6 +5088,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393493</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5005,6 +5215,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134394804</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5110,6 +5325,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395676</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5220,6 +5440,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395778</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5326,6 +5551,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134396010</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5433,6 +5663,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130466959</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5536,6 +5771,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134394521</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5639,6 +5879,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395609</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5742,6 +5987,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395789</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5845,6 +6095,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126848471</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5952,6 +6207,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130467040</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6070,6 +6330,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127748920</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6180,6 +6445,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134394466</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6293,6 +6563,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395971</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6398,6 +6673,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395945</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6501,6 +6781,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395409</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6608,6 +6893,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393436</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6715,6 +7005,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134393697</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6822,6 +7117,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395500</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6929,6 +7229,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134395824</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7036,6 +7341,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826277</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7143,6 +7453,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826308</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7245,6 +7560,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130466886</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7347,6 +7667,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130466908</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7450,8 +7775,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130466789</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>